--- a/liaisons_Super_Constellation/Reseau_Buffalo_L1049_sourced.xlsx
+++ b/liaisons_Super_Constellation/Reseau_Buffalo_L1049_sourced.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Grand Nord (illustratif)" sheetId="1" r:id="rId1"/>
+    <sheet name="Lignes DC-6" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H12"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -430,25 +430,25 @@
         <v>BF 101</v>
       </c>
       <c r="B2" t="str">
-        <v>Liaison du Grand Nord</v>
+        <v>Vallée du Mackenzie</v>
       </c>
       <c r="C2" t="str">
-        <v>Edmonton (YEG)</v>
+        <v>Yellowknife</v>
       </c>
       <c r="D2" t="str">
         <v>09:00</v>
       </c>
       <c r="E2" t="str">
-        <v>Yellowknife (11:30 / 12:30)</v>
+        <v>Norman Wells (11:30 / 12:15)</v>
       </c>
       <c r="F2" t="str">
-        <v>Churchill</v>
+        <v>Fort Good Hope</v>
       </c>
       <c r="G2" t="str">
-        <v>15:30</v>
+        <v>13:45</v>
       </c>
       <c r="H2" t="str">
-        <v>Lundi, Jeudi</v>
+        <v>Mardi, Vendredi</v>
       </c>
     </row>
     <row r="3">
@@ -456,77 +456,77 @@
         <v>BF 102</v>
       </c>
       <c r="B3" t="str">
-        <v>Liaison du Grand Nord (Retour)</v>
+        <v>Vallée du Mackenzie (Retour)</v>
       </c>
       <c r="C3" t="str">
-        <v>Churchill</v>
+        <v>Fort Good Hope</v>
       </c>
       <c r="D3" t="str">
         <v>14:00</v>
       </c>
       <c r="E3" t="str">
-        <v>Yellowknife (17:00 / 18:00)</v>
+        <v>Norman Wells (15:30 / 16:15)</v>
       </c>
       <c r="F3" t="str">
-        <v>Edmonton (YEG)</v>
+        <v>Yellowknife</v>
       </c>
       <c r="G3" t="str">
-        <v>20:30</v>
+        <v>18:45</v>
       </c>
       <c r="H3" t="str">
-        <v>Mardi, Vendredi</v>
+        <v>Mercredi, Samedi</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>BF 103</v>
+        <v>BF 120</v>
       </c>
       <c r="B4" t="str">
-        <v>Navette Arctique</v>
+        <v>Yellowknife – Hay River</v>
       </c>
       <c r="C4" t="str">
         <v>Yellowknife</v>
       </c>
       <c r="D4" t="str">
-        <v>10:00</v>
+        <v>08:00</v>
       </c>
       <c r="E4" t="str">
-        <v>Churchill (13:00 / 14:00)</v>
+        <v>Hay River (09:00 / 09:40)</v>
       </c>
       <c r="F4" t="str">
-        <v>Frobisher Bay</v>
+        <v>Edmonton (YEG)</v>
       </c>
       <c r="G4" t="str">
-        <v>19:00</v>
+        <v>12:10</v>
       </c>
       <c r="H4" t="str">
-        <v>Mercredi</v>
+        <v>Lundi, Jeudi</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>BF 104</v>
+        <v>BF 121</v>
       </c>
       <c r="B5" t="str">
-        <v>Navette Arctique (Retour)</v>
+        <v>Yellowknife – Hay River (Retour)</v>
       </c>
       <c r="C5" t="str">
-        <v>Frobisher Bay</v>
+        <v>Edmonton (YEG)</v>
       </c>
       <c r="D5" t="str">
-        <v>13:00</v>
+        <v>16:00</v>
       </c>
       <c r="E5" t="str">
-        <v>Churchill (18:00 / 19:00)</v>
+        <v>Hay River (18:30 / 19:10)</v>
       </c>
       <c r="F5" t="str">
         <v>Yellowknife</v>
       </c>
       <c r="G5" t="str">
-        <v>22:00</v>
+        <v>20:10</v>
       </c>
       <c r="H5" t="str">
-        <v>Samedi</v>
+        <v>Mardi, Vendredi</v>
       </c>
     </row>
     <row r="6">
@@ -583,7 +583,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>ATTENTION : Buffalo Airways est un transporteur canadien moderne (Grand Nord) qui n'a JAMAIS exploité le L-1049. Ce feuillet est fourni pour parité avec l'appli ; il est ENTIÈREMENT RECONSTITUÉ [R] et illustratif.</v>
+        <v>Sources : Buffalo Airways (Grand Nord canadien) exploite des Douglas DC-4 et possède un DC-6 « Swingtail » ; réseau de fret et de passagers dans les Territoires du Nord-Ouest.</v>
       </c>
       <c r="B8" t="str">
         <v/>
@@ -609,7 +609,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>[R] Aucune donnée sourcée : compagnie/appareil non historiques pour le L-1049.</v>
+        <v>Ligne exploitée historiquement en Douglas DC-6 ; proposée ici pour le Super Constellation L-1049, appareil de même catégorie (quadrimoteur à pistons long-courrier).</v>
       </c>
       <c r="B9" t="str">
         <v/>
@@ -635,7 +635,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>* Arrivée un jour plus tard (chaque * = +1 jour). [Tech] = escale technique. HL : Heure locale.</v>
+        <v>[R] Reconstitué : numéros de vol et horaires — non issus d'un timetable original.</v>
       </c>
       <c r="B10" t="str">
         <v/>
@@ -661,33 +661,59 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
+        <v>* Arrivée un jour plus tard (chaque * = +1 jour). [Tech] = escale technique. HL : Heure locale.</v>
+      </c>
+      <c r="B11" t="str">
+        <v/>
+      </c>
+      <c r="C11" t="str">
+        <v/>
+      </c>
+      <c r="D11" t="str">
+        <v/>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
         <v>[R] Vols retour reconstitués par itinéraire miroir (horaires plausibles).</v>
       </c>
-      <c r="B11" t="str">
-        <v/>
-      </c>
-      <c r="C11" t="str">
-        <v/>
-      </c>
-      <c r="D11" t="str">
-        <v/>
-      </c>
-      <c r="E11" t="str">
-        <v/>
-      </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
-      <c r="G11" t="str">
-        <v/>
-      </c>
-      <c r="H11" t="str">
+      <c r="B12" t="str">
+        <v/>
+      </c>
+      <c r="C12" t="str">
+        <v/>
+      </c>
+      <c r="D12" t="str">
+        <v/>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H12"/>
   </ignoredErrors>
 </worksheet>
 </file>